--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/report-service/getMemberProgressReport-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/report-service/getMemberProgressReport-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="96">
-  <si>
-    <t>Statement: ReportService.getMemberProgressReport(memberId, startDate, endDate) – Fetches member (throws NotFoundError if absent). Fetches all sessions in date range. Aggregates in-memory: per-exercise stats (totalSets, totalReps, totalVolume=sets×reps×weight, sessionCount via Set deduplication), per-session totals, overall totalVolume and averageSessionDuration. Returns exerciseBreakdown sorted descending by totalVolume.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="42">
+  <si>
+    <t>Statement: ReportService.getMemberProgressReport(id, start, end)</t>
   </si>
   <si>
     <t/>
@@ -31,26 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: memberId: string, startDate: Date, endDate: Date</t>
+    <t>Input: id, start, end</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>workoutSessionRepository and userRepository are accessible</t>
+    <t>repos accessible</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;Report&gt;  OR  throws NotFoundError</t>
+    <t>Output: report</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t xml:space="preserve">On success: returns Report with all aggregated statistics.
-On NotFoundError: no state change.</t>
+    <t>Generated.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -65,36 +64,6 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>member existence</t>
-  </si>
-  <si>
-    <t>member with given memberId exists</t>
-  </si>
-  <si>
-    <t>no member with given memberId (NotFoundError)</t>
-  </si>
-  <si>
-    <t>sessions in range</t>
-  </si>
-  <si>
-    <t>one or more sessions in date range</t>
-  </si>
-  <si>
-    <t>no sessions in date range (zero stats)</t>
-  </si>
-  <si>
-    <t>aggregation</t>
-  </si>
-  <si>
-    <t>multiple sessions with same exercise → sessionCount via Set deduplication</t>
-  </si>
-  <si>
-    <t>sorting</t>
-  </si>
-  <si>
-    <t>exerciseBreakdown sorted descending by totalVolume</t>
-  </si>
-  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -110,160 +79,28 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Non-existent memberId</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
-  </si>
-  <si>
-    <t>1,4</t>
-  </si>
-  <si>
-    <t>Valid memberId, no sessions in range</t>
-  </si>
-  <si>
-    <t>totalSessions=0, totalVolume=0, averageSessionDuration=0, exerciseBreakdown=[]</t>
-  </si>
-  <si>
-    <t>1,3</t>
-  </si>
-  <si>
-    <t>1 session, 1 exercise: sets=3, reps=10, weight=50</t>
-  </si>
-  <si>
-    <t>totalVolume=1500, averageSessionDuration=duration of that session</t>
-  </si>
-  <si>
-    <t>1,3,5</t>
-  </si>
-  <si>
-    <t>2 sessions with same exercise</t>
-  </si>
-  <si>
-    <t>stat.sessionCount=2, totalSets and totalReps correctly summed</t>
-  </si>
-  <si>
-    <t>2 sessions with durations 60 and 90</t>
-  </si>
-  <si>
-    <t>averageSessionDuration=75</t>
-  </si>
-  <si>
-    <t>1,3,6</t>
-  </si>
-  <si>
-    <t>1 session with 2 exercises of different volumes</t>
-  </si>
-  <si>
-    <t>exerciseBreakdown[0] has higher totalVolume than exerciseBreakdown[1]</t>
-  </si>
-  <si>
-    <t>Valid member, valid range</t>
-  </si>
-  <si>
-    <t>Report.memberId and Report.memberName populated correctly</t>
-  </si>
-  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>sessions count</t>
-  </si>
-  <si>
-    <t>Boundary: 0 sessions → averageSessionDuration=0 (no divide-by-zero)</t>
-  </si>
-  <si>
-    <t>volume formula</t>
-  </si>
-  <si>
-    <t>sets=3, reps=10, weight=50 → volume = 3×10×50 = 1500</t>
-  </si>
-  <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1</t>
-  </si>
-  <si>
-    <t>No sessions in range</t>
-  </si>
-  <si>
-    <t>averageSessionDuration = 0 (not NaN or error)</t>
-  </si>
-  <si>
-    <t>BVA-2</t>
-  </si>
-  <si>
-    <t>1 session: sets=3, reps=10, weight=50</t>
-  </si>
-  <si>
-    <t>totalVolume = 1500</t>
-  </si>
-  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>Member exists, no sessions</t>
-  </si>
-  <si>
-    <t>All stats zero, no error</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>1 session sets=3 reps=10 weight=50</t>
-  </si>
-  <si>
-    <t>totalVolume=1500</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
-    <t>2 sessions same exercise</t>
-  </si>
-  <si>
-    <t>sessionCount=2, correct aggregate</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>Durations 60 &amp; 90</t>
-  </si>
-  <si>
-    <t>EP-6</t>
-  </si>
-  <si>
-    <t>2 exercises different volumes</t>
-  </si>
-  <si>
-    <t>Sorted descending by totalVolume</t>
-  </si>
-  <si>
-    <t>EP-7</t>
-  </si>
-  <si>
-    <t>Valid member and range</t>
-  </si>
-  <si>
-    <t>memberName populated</t>
+    <t>Report</t>
+  </si>
+  <si>
+    <t>Success/Error</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>Testing</t>
@@ -821,7 +658,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -843,90 +680,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -935,7 +688,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -947,138 +700,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1089,7 +723,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1099,35 +733,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1138,7 +750,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1150,53 +762,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1207,7 +785,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1220,22 +798,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1243,19 +821,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1263,19 +841,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1283,19 +861,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1303,19 +881,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1323,19 +901,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1343,19 +921,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1363,19 +941,119 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>81</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1403,16 +1081,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1420,45 +1098,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1467,19 +1145,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>95</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/report-service/getMemberProgressReport-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/report-service/getMemberProgressReport-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="42">
-  <si>
-    <t>Statement: ReportService.getMemberProgressReport(id, start, end)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="93">
+  <si>
+    <t>Statement: ReportService.getMemberProgressReport(memberId, startDate, endDate) – Generates a progress report for a member over a date range. Returns a report with memberId, memberName, totalSessions, totalVolume, averageSessionDuration, exerciseBreakdown (sorted by totalVolume DESC), sessionDetails, startDate, and endDate. Throws NotFoundError if the member does not exist.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: id, start, end</t>
+    <t>Input: memberId: string, startDate: Date, endDate: Date</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>repos accessible</t>
+    <t>The referenced member may or may not exist. Sessions in the given date range may or may not exist for that member.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: report</t>
+    <t>Output: Promise&lt;MemberProgressReport&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Generated.</t>
+    <t>On success: report returned with correct aggregates (totalSessions, totalVolume, averageSessionDuration), exerciseBreakdown sorted by totalVolume DESC, and sessionDetails listing each session. On failure: NotFoundError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,6 +64,36 @@
     <t>Invalid EC</t>
   </si>
   <si>
+    <t>Member existence</t>
+  </si>
+  <si>
+    <t>Member not found → NotFoundError</t>
+  </si>
+  <si>
+    <t>Session availability</t>
+  </si>
+  <si>
+    <t>No sessions in range → zero-stats report</t>
+  </si>
+  <si>
+    <t>Multiple sessions</t>
+  </si>
+  <si>
+    <t>Multiple sessions → correct totalSessions, totalVolume, averageSessionDuration, exerciseBreakdown, sessionDetails</t>
+  </si>
+  <si>
+    <t>Multiple exercises</t>
+  </si>
+  <si>
+    <t>Multiple exercises in one session → exerciseBreakdown.length: 2, correct per-exercise totalVolume, totalVolume sum</t>
+  </si>
+  <si>
+    <t>Sorting</t>
+  </si>
+  <si>
+    <t>Exercises with different volumes → exerciseBreakdown[0] has highest volume, exerciseBreakdown[0].totalVolume &gt; exerciseBreakdown[1].totalVolume</t>
+  </si>
+  <si>
     <t>No TC</t>
   </si>
   <si>
@@ -79,28 +109,151 @@
     <t>Actual Result</t>
   </si>
   <si>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID (not found), startDate: START_DATE, endDate: END_DATE</t>
+  </si>
+  <si>
+    <t>throws NotFoundError("Member not found")</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, startDate: START_DATE, endDate: END_DATE, sessions: []</t>
+  </si>
+  <si>
+    <t>report returned with memberId: MEMBER_ID, memberName: MOCK_MEMBER.user.fullName, totalSessions: 0, totalVolume: 0, averageSessionDuration: 0, exerciseBreakdown.length: 0, sessionDetails.length: 0</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, sessions: [60min 3×10×50, 90min 3×10×50]</t>
+  </si>
+  <si>
+    <t>report with totalSessions: 2, averageSessionDuration: 75, totalVolume: 3000, exerciseBreakdown.length: 1, exerciseBreakdown[0].exerciseId: EXERCISE_ID, exerciseBreakdown[0].sessionCount: 2, exerciseBreakdown[0].totalVolume: 3000, sessionDetails.length: 2, sessionDetails[0].sessionId: SESSION_ID_1, sessionDetails[1].sessionId: SESSION_ID_2</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, session: 1 session with ex-a (3×10×50) and ex-b (4×12×40)</t>
+  </si>
+  <si>
+    <t>report with exerciseBreakdown.length: 2, bench.totalVolume: 1500, ohp.totalVolume: 1920, totalVolume: 3420</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, session: ex-low (1×1×1) and ex-high (10×10×100)</t>
+  </si>
+  <si>
+    <t>report with exerciseBreakdown[0].exerciseId: "ex-high", exerciseBreakdown[1].exerciseId: "ex-low", exerciseBreakdown[0].totalVolume &gt; exerciseBreakdown[1].totalVolume</t>
+  </si>
+  <si>
     <t>Number BVA</t>
   </si>
   <si>
     <t>BVA Test Case</t>
   </si>
   <si>
+    <t>Member ID length</t>
+  </si>
+  <si>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
+  </si>
+  <si>
+    <t>Date range boundary</t>
+  </si>
+  <si>
+    <t>startDate equals endDate (same day)</t>
+  </si>
+  <si>
+    <t>Volume inputs</t>
+  </si>
+  <si>
+    <t>weight: 0 (volume = 0), reps: 0 (volume = 0)</t>
+  </si>
+  <si>
+    <t>Session duration</t>
+  </si>
+  <si>
+    <t>duration: 0 (averageSessionDuration: 0)</t>
+  </si>
+  <si>
     <t>BVA</t>
   </si>
   <si>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>memberId: "", startDate: START_DATE, endDate: END_DATE</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>memberId: "a" (no match), startDate: START_DATE, endDate: END_DATE</t>
+  </si>
+  <si>
+    <t>memberId: "a" (found), startDate: START_DATE, endDate: END_DATE, sessions: []</t>
+  </si>
+  <si>
+    <t>report returned with memberId: "a", totalSessions: 0</t>
+  </si>
+  <si>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, startDate: 2024-06-15, endDate: 2024-06-15, sessions: []</t>
+  </si>
+  <si>
+    <t>report returned with startDate: 2024-06-15, endDate: 2024-06-15</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, session: makeSession(60, 3, 10, weight=0)</t>
+  </si>
+  <si>
+    <t>report with totalVolume: 0, exerciseBreakdown[0].totalVolume: 0</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, session: makeSession(60, 3, reps=0, 50)</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, session: makeSession(duration=0, 3, 10, 50)</t>
+  </si>
+  <si>
+    <t>report with averageSessionDuration: 0, totalSessions: 1</t>
+  </si>
+  <si>
     <t>TC from EC</t>
   </si>
   <si>
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Report</t>
-  </si>
-  <si>
-    <t>Success/Error</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>report with memberId: MEMBER_ID, memberName: MOCK_MEMBER.user.fullName, totalSessions: 0, totalVolume: 0, averageSessionDuration: 0, exerciseBreakdown.length: 0, sessionDetails.length: 0</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, session with ex-a (3×10×50) and ex-b (4×12×40)</t>
+  </si>
+  <si>
+    <t>memberId: MEMBER_ID, session with ex-low (1×1×1) and ex-high (10×10×100)</t>
+  </si>
+  <si>
+    <t>BVA-1</t>
   </si>
   <si>
     <t>Testing</t>
@@ -133,7 +286,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>RPG-01</t>
+    <t>SERV-28</t>
   </si>
   <si>
     <t>n/a</t>
@@ -658,7 +811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -680,6 +833,76 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -688,7 +911,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -700,19 +923,104 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -723,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -733,13 +1041,57 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>21</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +1102,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -762,19 +1114,138 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -798,22 +1269,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -821,19 +1292,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -841,19 +1312,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -861,19 +1332,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -881,19 +1352,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -901,19 +1372,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -921,19 +1392,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -941,19 +1412,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -961,19 +1432,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -981,19 +1452,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1001,19 +1472,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1021,19 +1492,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1041,19 +1512,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1081,16 +1552,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1098,39 +1569,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="B3" s="1">
         <v>12</v>
@@ -1145,19 +1616,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/service/__tests__/bbt/report-service/getMemberProgressReport-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/service/__tests__/bbt/report-service/getMemberProgressReport-bbt-form.xlsx
@@ -286,7 +286,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SERV-28</t>
+    <t>SERV-29</t>
   </si>
   <si>
     <t>n/a</t>
